--- a/teams-and-rosters/CS320-Sp25-Teams.xlsx
+++ b/teams-and-rosters/CS320-Sp25-Teams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D3AC61-58D7-4ECA-AE6B-3ECEDA63DEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E03C4E-FCBB-4947-A103-8BF80B983F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1935" windowWidth="21480" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="645" yWindow="615" windowWidth="22050" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>CS320: Software Engineering Teams - Spring 2025</t>
-  </si>
-  <si>
-    <t>In-Class Mentors: TBD</t>
   </si>
   <si>
     <t>Team 101-1:
@@ -67,6 +64,12 @@
   </si>
   <si>
     <t>Section 102 - BABCOCK (M-W-F: 3:00 to 3:50)</t>
+  </si>
+  <si>
+    <t>In-Class Mentors: Emmett Larsen (CS-Jr)</t>
+  </si>
+  <si>
+    <t>In-Class Mentor: Brandon Woodward (CS-Jr)</t>
   </si>
 </sst>
 </file>
@@ -644,7 +647,7 @@
     </row>
     <row r="4" spans="2:6" ht="21" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
@@ -653,7 +656,7 @@
     </row>
     <row r="5" spans="2:6" s="4" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="18" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -662,16 +665,16 @@
     </row>
     <row r="6" spans="2:6" s="2" customFormat="1" ht="48.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>4</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -707,7 +710,7 @@
     <row r="12" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:6" ht="21" x14ac:dyDescent="0.35">
       <c r="B13" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
@@ -716,7 +719,7 @@
     </row>
     <row r="14" spans="2:6" s="4" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -725,16 +728,16 @@
     </row>
     <row r="15" spans="2:6" ht="33" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="E15" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">

--- a/teams-and-rosters/CS320-Sp25-Teams.xlsx
+++ b/teams-and-rosters/CS320-Sp25-Teams.xlsx
@@ -8,35 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E03C4E-FCBB-4947-A103-8BF80B983F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE7408A-8B73-4A55-B007-D747DF2937F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="645" yWindow="615" windowWidth="22050" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1335" yWindow="630" windowWidth="15405" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Projects" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>CS320: Software Engineering Teams - Spring 2025</t>
-  </si>
-  <si>
-    <t>Team 101-1:
-???</t>
-  </si>
-  <si>
-    <t>Team 101-2:
-???</t>
-  </si>
-  <si>
-    <t>Team 101-3:
-???</t>
   </si>
   <si>
     <t xml:space="preserve">Team 101-4:
@@ -44,18 +30,6 @@
 </t>
   </si>
   <si>
-    <t>Team 102-1:
-???</t>
-  </si>
-  <si>
-    <t>Team 102-2:
-???</t>
-  </si>
-  <si>
-    <t>Team 102-3:
-???</t>
-  </si>
-  <si>
     <t>Team 102-4:
 ???</t>
   </si>
@@ -66,10 +40,115 @@
     <t>Section 102 - BABCOCK (M-W-F: 3:00 to 3:50)</t>
   </si>
   <si>
-    <t>In-Class Mentors: Emmett Larsen (CS-Jr)</t>
-  </si>
-  <si>
-    <t>In-Class Mentor: Brandon Woodward (CS-Jr)</t>
+    <t>Team 102-2:
+RevMetrix UI &amp; DB</t>
+  </si>
+  <si>
+    <t>Team 102-3:
+ABET Assessment App</t>
+  </si>
+  <si>
+    <t>Team 101-2:
+TBAG: YCP Finals Frenzy</t>
+  </si>
+  <si>
+    <t>Team 101-1:
+TBAG:
+The Green Light District</t>
+  </si>
+  <si>
+    <t>Team 101-3:
+TBAG:
+&lt;Your Project/Application Name Here&gt;</t>
+  </si>
+  <si>
+    <t>Team 102-1:
+TBAG:
+Every Breath You Take</t>
+  </si>
+  <si>
+    <t>Andrew Olvera</t>
+  </si>
+  <si>
+    <t>Derek Martin</t>
+  </si>
+  <si>
+    <t>Dylan Parise</t>
+  </si>
+  <si>
+    <t>Ethan Nelson</t>
+  </si>
+  <si>
+    <t>Joe Zink</t>
+  </si>
+  <si>
+    <t>Brandon Marcelo</t>
+  </si>
+  <si>
+    <t>Ethan Pate</t>
+  </si>
+  <si>
+    <t>Noah McFarland</t>
+  </si>
+  <si>
+    <t>Andrew Hellmann</t>
+  </si>
+  <si>
+    <t>Evan Natale</t>
+  </si>
+  <si>
+    <t>Nadia Hanna</t>
+  </si>
+  <si>
+    <t>Logan Kinzler</t>
+  </si>
+  <si>
+    <t>Aidan Lynch</t>
+  </si>
+  <si>
+    <t>Matthew Voithofer</t>
+  </si>
+  <si>
+    <t>Thomas Wakeland</t>
+  </si>
+  <si>
+    <t>Alyssa Nelson</t>
+  </si>
+  <si>
+    <t>Caroline Young</t>
+  </si>
+  <si>
+    <t>Olivia Hornbeck</t>
+  </si>
+  <si>
+    <t>Jackson Harvey</t>
+  </si>
+  <si>
+    <t>Tucker Davis</t>
+  </si>
+  <si>
+    <t>William Galasso</t>
+  </si>
+  <si>
+    <t>Jeremiah Maldonado</t>
+  </si>
+  <si>
+    <t>Tanner Sweigert</t>
+  </si>
+  <si>
+    <t>Collin Reppert</t>
+  </si>
+  <si>
+    <t>Ethan Onyejesi</t>
+  </si>
+  <si>
+    <t>Shaan Patel</t>
+  </si>
+  <si>
+    <t>In-Class Mentor: Brandon Woodward (CS-Jr) - see Canvas for Contact Information and Hours</t>
+  </si>
+  <si>
+    <t>In-Class Mentors: Emmett Larsen (CS-Jr) - see Canvas for Contact Information and Hours</t>
   </si>
 </sst>
 </file>
@@ -647,7 +726,7 @@
     </row>
     <row r="4" spans="2:6" ht="21" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
@@ -656,61 +735,87 @@
     </row>
     <row r="5" spans="2:6" s="4" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="18" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="2:6" s="2" customFormat="1" ht="48.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" s="2" customFormat="1" ht="80.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="14"/>
+      <c r="B7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="14"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="E8" s="9"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="E9" s="9"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="E10" s="9"/>
     </row>
     <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
+      <c r="C11" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:6" ht="21" x14ac:dyDescent="0.35">
       <c r="B13" s="19" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
@@ -719,54 +824,80 @@
     </row>
     <row r="14" spans="2:6" s="4" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" ht="33" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="48.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>7</v>
-      </c>
       <c r="E15" s="13" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="E16" s="14"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="E17" s="9"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="E18" s="9"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="E19" s="15"/>
     </row>
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="16"/>
-      <c r="C20" s="11"/>
+      <c r="C20" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D20" s="11"/>
       <c r="E20" s="16"/>
     </row>
@@ -783,22 +914,4 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/teams-and-rosters/CS320-Sp25-Teams.xlsx
+++ b/teams-and-rosters/CS320-Sp25-Teams.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE7408A-8B73-4A55-B007-D747DF2937F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F48E11D-E46B-48CD-BB71-13552A1FC9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1335" yWindow="630" windowWidth="15405" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -742,7 +755,7 @@
       <c r="E5" s="18"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="2:6" s="2" customFormat="1" ht="80.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" s="2" customFormat="1" ht="86.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
@@ -831,7 +844,7 @@
       <c r="E14" s="18"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" ht="48.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="58.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
         <v>10</v>
       </c>

--- a/teams-and-rosters/CS320-Sp25-Teams.xlsx
+++ b/teams-and-rosters/CS320-Sp25-Teams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F48E11D-E46B-48CD-BB71-13552A1FC9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEDFA93-4537-4540-A22E-58E48D566926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="630" windowWidth="15405" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="360" windowWidth="22935" windowHeight="14970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
@@ -70,11 +70,6 @@
 The Green Light District</t>
   </si>
   <si>
-    <t>Team 101-3:
-TBAG:
-&lt;Your Project/Application Name Here&gt;</t>
-  </si>
-  <si>
     <t>Team 102-1:
 TBAG:
 Every Breath You Take</t>
@@ -162,6 +157,10 @@
   </si>
   <si>
     <t>In-Class Mentors: Emmett Larsen (CS-Jr) - see Canvas for Contact Information and Hours</t>
+  </si>
+  <si>
+    <t>Team 101-3:
+TBAG: Nine to Thrive</t>
   </si>
 </sst>
 </file>
@@ -748,7 +747,7 @@
     </row>
     <row r="5" spans="2:6" s="4" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -763,7 +762,7 @@
         <v>7</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>1</v>
@@ -771,56 +770,56 @@
     </row>
     <row r="7" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="14"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="9"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="9"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" s="9"/>
     </row>
     <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
@@ -837,7 +836,7 @@
     </row>
     <row r="14" spans="2:6" s="4" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -846,7 +845,7 @@
     </row>
     <row r="15" spans="2:6" ht="58.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>5</v>
@@ -860,56 +859,56 @@
     </row>
     <row r="16" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="14"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" s="9"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" s="9"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" s="15"/>
     </row>
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="16"/>
       <c r="C20" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="16"/>
